--- a/tests/fixtures/merge/merge-pattern-sample01.xlsx
+++ b/tests/fixtures/merge/merge-pattern-sample01.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10308"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/igapyon/Documents/git/local-html-tools/docs/xlsx2md/tests/fixtures/merge/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/igapyon/Documents/git/xlsx2md/tests/fixtures/merge/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F964E88-B983-4E4C-A23F-CA9B15C9A2AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
@@ -291,28 +291,28 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -678,25 +678,25 @@
       <c r="A2" s="2">
         <v>1</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="5"/>
-      <c r="D2" s="4" t="s">
+      <c r="C2" s="7"/>
+      <c r="D2" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="5"/>
+      <c r="E2" s="7"/>
     </row>
     <row r="3" spans="1:5" ht="20">
       <c r="A3" s="2">
         <f>A2+1</f>
         <v>2</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="6"/>
-      <c r="D3" s="5"/>
+      <c r="C3" s="8"/>
+      <c r="D3" s="7"/>
       <c r="E3" s="2" t="s">
         <v>7</v>
       </c>
@@ -706,12 +706,12 @@
         <f>A3+1</f>
         <v>3</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="6"/>
-      <c r="D4" s="6"/>
-      <c r="E4" s="5"/>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="7"/>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="1" t="s">
@@ -736,13 +736,13 @@
       <c r="A8" s="2">
         <v>1</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="C8" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="D8" s="7" t="s">
+      <c r="D8" s="9" t="s">
         <v>8</v>
       </c>
     </row>
@@ -751,31 +751,31 @@
         <f>A8+1</f>
         <v>2</v>
       </c>
-      <c r="B9" s="8"/>
-      <c r="C9" s="9"/>
-      <c r="D9" s="9"/>
+      <c r="B9" s="10"/>
+      <c r="C9" s="11"/>
+      <c r="D9" s="11"/>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2">
         <f>A9+1</f>
         <v>3</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="8"/>
-      <c r="D10" s="9"/>
+      <c r="C10" s="10"/>
+      <c r="D10" s="11"/>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2">
         <f>A10+1</f>
         <v>4</v>
       </c>
-      <c r="B11" s="8"/>
+      <c r="B11" s="10"/>
       <c r="C11" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D11" s="8"/>
+      <c r="D11" s="10"/>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="1" t="s">
@@ -803,48 +803,48 @@
       <c r="A15" s="2">
         <v>1</v>
       </c>
-      <c r="B15" s="10" t="s">
+      <c r="B15" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C15" s="11"/>
-      <c r="D15" s="10" t="s">
+      <c r="C15" s="5"/>
+      <c r="D15" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E15" s="11"/>
+      <c r="E15" s="5"/>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="2">
         <f>A15+1</f>
         <v>2</v>
       </c>
-      <c r="B16" s="11"/>
-      <c r="C16" s="11"/>
-      <c r="D16" s="11"/>
-      <c r="E16" s="11"/>
+      <c r="B16" s="5"/>
+      <c r="C16" s="5"/>
+      <c r="D16" s="5"/>
+      <c r="E16" s="5"/>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="2">
         <f>A16+1</f>
         <v>3</v>
       </c>
-      <c r="B17" s="10" t="s">
+      <c r="B17" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C17" s="11"/>
-      <c r="D17" s="10" t="s">
+      <c r="C17" s="5"/>
+      <c r="D17" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E17" s="11"/>
+      <c r="E17" s="5"/>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="2">
         <f>A17+1</f>
         <v>4</v>
       </c>
-      <c r="B18" s="11"/>
-      <c r="C18" s="11"/>
-      <c r="D18" s="11"/>
-      <c r="E18" s="11"/>
+      <c r="B18" s="5"/>
+      <c r="C18" s="5"/>
+      <c r="D18" s="5"/>
+      <c r="E18" s="5"/>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="1" t="s">

--- a/tests/fixtures/merge/merge-pattern-sample01.xlsx
+++ b/tests/fixtures/merge/merge-pattern-sample01.xlsx
@@ -3,11 +3,6 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
   <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/igapyon/Documents/git/xlsx2md/tests/fixtures/merge/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F964E88-B983-4E4C-A23F-CA9B15C9A2AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1200" yWindow="600" windowWidth="27340" windowHeight="16760" xr2:uid="{95EFFC77-0BB9-C24C-8C40-5FB8F9D33BDC}"/>
